--- a/tame_output/ON/bt/strategyON_20240925.xlsx
+++ b/tame_output/ON/bt/strategyON_20240925.xlsx
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-574.5%</t>
+          <t>-574.6%</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-48.9%</t>
+          <t>-49.0%</t>
         </is>
       </c>
     </row>
@@ -49782,10 +49782,10 @@
         <v>4.925091228059886</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.129734128024577</v>
+        <v>-4.130723124374258</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.272841152536307</v>
+        <v>3.272445553996435</v>
       </c>
       <c r="F2097" t="n">
         <v>1.638215498407577</v>

--- a/tame_output/ON/bt/strategyON_20240925.xlsx
+++ b/tame_output/ON/bt/strategyON_20240925.xlsx
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-75.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.4%</t>
+          <t>108.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.6%</t>
+          <t>123.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.4%</t>
+          <t>-71.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.3%</t>
+          <t>420.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-574.6%</t>
+          <t>-588.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-49.0%</t>
+          <t>-54.5%</t>
         </is>
       </c>
     </row>
@@ -49408,7 +49408,7 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.647907242740921</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
@@ -49431,7 +49431,7 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.881065366663624</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
@@ -49454,7 +49454,7 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424768</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
@@ -49477,7 +49477,7 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149217</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
@@ -49500,7 +49500,7 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383091</v>
+        <v>3.73530072138309</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
@@ -49523,7 +49523,7 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720997</v>
+        <v>3.778232147720996</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
@@ -49546,7 +49546,7 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455271</v>
+        <v>3.77535709745527</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
@@ -49569,7 +49569,7 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963132</v>
+        <v>3.749078058963131</v>
       </c>
       <c r="C2088" t="n">
         <v>4.514368785453932</v>
@@ -49592,7 +49592,7 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162542</v>
+        <v>3.740284389162541</v>
       </c>
       <c r="C2089" t="n">
         <v>4.516370299108037</v>
@@ -49782,10 +49782,10 @@
         <v>4.925091228059886</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.130723124374258</v>
+        <v>-4.26766591996594</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.272445553996435</v>
+        <v>3.217668435759762</v>
       </c>
       <c r="F2097" t="n">
         <v>1.638215498407577</v>

--- a/tame_output/ON/bt/strategyON_20240925.xlsx
+++ b/tame_output/ON/bt/strategyON_20240925.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>36.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>115.1%</t>
+          <t>115.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,22 +786,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-43.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>100.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>182.6%</t>
+          <t>187.0%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-74.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,16 +926,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.8%</t>
+          <t>123.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>92.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.1%</t>
+          <t>-69.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.8%</t>
+          <t>420.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-588.9%</t>
+          <t>-562.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,37 +1160,37 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-53.0%</t>
+          <t>-37.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>114.1%</t>
+          <t>111.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-319.9%</t>
+          <t>-320.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-47.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>133.3%</t>
+          <t>140.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>121.8%</t>
+          <t>132.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>138.1%</t>
+          <t>158.4%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2097"/>
+  <dimension ref="A1:G2098"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45340,19 +45340,19 @@
         <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.155859013848905</v>
+        <v>3.024132103905334</v>
       </c>
       <c r="D1904" t="n">
         <v>-6.867595175047173</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4084645195162873</v>
+        <v>0.276737609572717</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.6459819352748123</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.768269852684018</v>
+        <v>2.636542942740447</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.057119799856059</v>
+        <v>2.925392889912489</v>
       </c>
       <c r="D1905" t="n">
         <v>-6.735319701416286</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3626354949757968</v>
+        <v>0.2309085850322266</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.5137064616439256</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.748895922869704</v>
+        <v>2.617169012926134</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.059934860543696</v>
+        <v>2.928207950600126</v>
       </c>
       <c r="D1906" t="n">
         <v>-6.563458485851384</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4341950418893945</v>
+        <v>0.3024681319458242</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.3418452460790228</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.854827712896283</v>
+        <v>2.723100802952712</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.072841201767355</v>
+        <v>2.941114291823784</v>
       </c>
       <c r="D1907" t="n">
         <v>-6.478493819122065</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4810872498047809</v>
+        <v>0.3493603398612106</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.2568805793497032</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.918712854157533</v>
+        <v>2.786985944213963</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
-        <v>2.944865272168136</v>
+        <v>2.813138362224565</v>
       </c>
       <c r="D1908" t="n">
         <v>-6.584083808895169</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3108753242963203</v>
+        <v>0.1791484143527495</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.3624705691228076</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.727382930694452</v>
+        <v>2.595656020750881</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
-        <v>2.993409614045222</v>
+        <v>2.861682704101652</v>
       </c>
       <c r="D1909" t="n">
         <v>-6.515849224269742</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3867135000235775</v>
+        <v>0.2549865900800068</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.3440552462502716</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.78697646629506</v>
+        <v>2.655249556351489</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.876788805406815</v>
+        <v>2.745061895463245</v>
       </c>
       <c r="D1910" t="n">
         <v>-6.367909182862142</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3292687079482102</v>
+        <v>0.1975417980046394</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.323734330341714</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.682548207201787</v>
+        <v>2.550821297258217</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.868074819153337</v>
+        <v>2.736347909209766</v>
       </c>
       <c r="D1911" t="n">
         <v>-6.314939660608154</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3417425305963278</v>
+        <v>0.210015620652757</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.2707648080877251</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.705615934300702</v>
+        <v>2.573889024357132</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.861114207058244</v>
+        <v>2.729387297114673</v>
       </c>
       <c r="D1912" t="n">
         <v>-6.149151464647863</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4010971968853507</v>
+        <v>0.26937028694178</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.2707648080877251</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.698655322205609</v>
+        <v>2.566928412262039</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.875576561439387</v>
+        <v>2.743849651495816</v>
       </c>
       <c r="D1913" t="n">
         <v>-6.115788258169094</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4289048338580015</v>
+        <v>0.2971779239144308</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.2707648080877251</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.713117676586752</v>
+        <v>2.581390766643182</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.870108681898582</v>
+        <v>2.738381771955011</v>
       </c>
       <c r="D1914" t="n">
         <v>-6.007529121046573</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4667406091662052</v>
+        <v>0.3350136992226345</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.2707648080877251</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.707649797045947</v>
+        <v>2.575922887102377</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.867606775909159</v>
+        <v>2.735879865965588</v>
       </c>
       <c r="D1915" t="n">
         <v>-5.884237986229442</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5135551571036343</v>
+        <v>0.3818282471600636</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.1474736732705946</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.779122571946802</v>
+        <v>2.647395662003232</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.875307754146484</v>
+        <v>2.743580844202913</v>
       </c>
       <c r="D1916" t="n">
         <v>-5.831541119098151</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5423348821934759</v>
+        <v>0.4106079722499052</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.09477680613930345</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.818441670462903</v>
+        <v>2.686714760519332</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.871088462493535</v>
+        <v>2.739361552549964</v>
       </c>
       <c r="D1917" t="n">
         <v>-5.587775677114706</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6356217673339044</v>
+        <v>0.5038948573903337</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.09477680613930345</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.814222378809953</v>
+        <v>2.682495468866382</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.873212776413551</v>
+        <v>2.74148586646998</v>
       </c>
       <c r="D1918" t="n">
         <v>-5.498000004738234</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6736563502045092</v>
+        <v>0.5419294402609385</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.03317736122499343</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.853306359678555</v>
+        <v>2.721579449734985</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.865954851397253</v>
+        <v>2.734227941453682</v>
       </c>
       <c r="D1919" t="n">
         <v>-5.248149610789159</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7663385827678413</v>
+        <v>0.6346116728242706</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.03317736122499343</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.846048434662257</v>
+        <v>2.714321524718687</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.869553974917902</v>
+        <v>2.737827064974331</v>
       </c>
       <c r="D1920" t="n">
         <v>-5.072257518321727</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8402945432754629</v>
+        <v>0.7085676333318922</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.03317736122499343</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.849647558182906</v>
+        <v>2.717920648239335</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.882881480972455</v>
+        <v>2.751154571028885</v>
       </c>
       <c r="D1921" t="n">
         <v>-4.900811055299264</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9222006345390019</v>
+        <v>0.7904737245954312</v>
       </c>
       <c r="F1921" t="n">
         <v>0.1382691017974697</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.965842942050938</v>
+        <v>2.834116032107367</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.881901958588752</v>
+        <v>2.750175048645182</v>
       </c>
       <c r="D1922" t="n">
         <v>-4.820788768190143</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9532300269989473</v>
+        <v>0.8215031170553766</v>
       </c>
       <c r="F1922" t="n">
         <v>0.2182913889065907</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.012876791932707</v>
+        <v>2.881149881989137</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.88659675964307</v>
+        <v>2.754869849699499</v>
       </c>
       <c r="D1923" t="n">
         <v>-4.757153025956208</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9833791249468384</v>
+        <v>0.8516522150032677</v>
       </c>
       <c r="F1923" t="n">
         <v>0.2819271311405252</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.055753038327385</v>
+        <v>2.924026128383814</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.867791018426865</v>
+        <v>2.736064108483295</v>
       </c>
       <c r="D1924" t="n">
         <v>-4.663455707739813</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.002052311017192</v>
+        <v>0.8703254010736212</v>
       </c>
       <c r="F1924" t="n">
         <v>0.2819271311405252</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.036947297111181</v>
+        <v>2.90522038716761</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.869534095051743</v>
+        <v>2.737807185108172</v>
       </c>
       <c r="D1925" t="n">
         <v>-4.673958330805102</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9995943384159538</v>
+        <v>0.8678674284723831</v>
       </c>
       <c r="F1925" t="n">
         <v>0.2714245080752363</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.032388799896885</v>
+        <v>2.900661889953314</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.873463408886563</v>
+        <v>2.741736498942992</v>
       </c>
       <c r="D1926" t="n">
         <v>-4.561472070136228</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.048518156518324</v>
+        <v>0.9167912465747532</v>
       </c>
       <c r="F1926" t="n">
         <v>0.2714245080752363</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.036318113731705</v>
+        <v>2.904591203788134</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.874141992803903</v>
+        <v>2.742415082860332</v>
       </c>
       <c r="D1927" t="n">
         <v>-4.543758383258362</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.05628221518681</v>
+        <v>0.9245553052432394</v>
       </c>
       <c r="F1927" t="n">
         <v>0.2746058369721531</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.038905494987195</v>
+        <v>2.907178585043624</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848616626502333</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.871140064023896</v>
+        <v>2.739413154080326</v>
       </c>
       <c r="D1928" t="n">
         <v>-4.420284111945344</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.102669994932011</v>
+        <v>0.97094308498844</v>
       </c>
       <c r="F1928" t="n">
         <v>0.2746058369721531</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.035903566207188</v>
+        <v>2.904176656263618</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.872719101034511</v>
+        <v>2.74099219109094</v>
       </c>
       <c r="D1929" t="n">
         <v>-4.200263313908334</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.192257351157429</v>
+        <v>1.060530441213858</v>
       </c>
       <c r="F1929" t="n">
         <v>0.4158256820401334</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.122214510258591</v>
+        <v>2.99048760031502</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.888613283836334</v>
+        <v>2.756886373892763</v>
       </c>
       <c r="D1930" t="n">
         <v>-4.067395624845056</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.261298609584564</v>
+        <v>1.129571699640993</v>
       </c>
       <c r="F1930" t="n">
         <v>0.4158256820401334</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.138108693060414</v>
+        <v>3.006381783116844</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.889759128276636</v>
+        <v>2.758032218333065</v>
       </c>
       <c r="D1931" t="n">
         <v>-3.947222541480557</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.310513687370665</v>
+        <v>1.178786777427094</v>
       </c>
       <c r="F1931" t="n">
         <v>0.5359987654046323</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.211358387519415</v>
+        <v>3.079631477575845</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.899847230838076</v>
+        <v>2.768120320894505</v>
       </c>
       <c r="D1932" t="n">
         <v>-3.81196918015058</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.374703134464096</v>
+        <v>1.242976224520525</v>
       </c>
       <c r="F1932" t="n">
         <v>0.6712521267346094</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.302598506878842</v>
+        <v>3.170871596935271</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.885884722239501</v>
+        <v>2.754157812295931</v>
       </c>
       <c r="D1933" t="n">
         <v>-3.871844007508273</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.336790694922444</v>
+        <v>1.205063784978874</v>
       </c>
       <c r="F1933" t="n">
         <v>0.6113772993769173</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.252711101865652</v>
+        <v>3.120984191922081</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.90117389147371</v>
+        <v>2.769446981530139</v>
       </c>
       <c r="D1934" t="n">
         <v>-3.752023776597435</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.400007956520988</v>
+        <v>1.268281046577417</v>
       </c>
       <c r="F1934" t="n">
         <v>0.6113772993769173</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.268000271099861</v>
+        <v>3.13627336115629</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.808818090796152</v>
+        <v>2.677091180852581</v>
       </c>
       <c r="D1935" t="n">
         <v>-3.754493483059241</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.306664273258707</v>
+        <v>1.174937363315136</v>
       </c>
       <c r="F1935" t="n">
         <v>0.6089075929151111</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.174162646545219</v>
+        <v>3.042435736601648</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.728079952281453</v>
+        <v>2.596353042337882</v>
       </c>
       <c r="D1936" t="n">
         <v>-3.822863669383251</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.198578060214404</v>
+        <v>1.066851150270834</v>
       </c>
       <c r="F1936" t="n">
         <v>0.618183291951326</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.098989927452249</v>
+        <v>2.967263017508678</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.718516660913344</v>
+        <v>2.586789750969773</v>
       </c>
       <c r="D1937" t="n">
         <v>-3.934735949009402</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.144265856995835</v>
+        <v>1.012538947052265</v>
       </c>
       <c r="F1937" t="n">
         <v>0.618183291951326</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.08942663608414</v>
+        <v>2.957699726140569</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.685091185837372</v>
+        <v>2.553364275893801</v>
       </c>
       <c r="D1938" t="n">
         <v>-3.918761283523134</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.11723024811437</v>
+        <v>0.9855033381707994</v>
       </c>
       <c r="F1938" t="n">
         <v>0.618183291951326</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.056001161008167</v>
+        <v>2.924274251064597</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.689658417829159</v>
+        <v>2.557931507885589</v>
       </c>
       <c r="D1939" t="n">
         <v>-3.743287023730665</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.191987184023146</v>
+        <v>1.060260274079575</v>
       </c>
       <c r="F1939" t="n">
         <v>0.618183291951326</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.060568392999955</v>
+        <v>2.928841483056384</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225438</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.665400446590366</v>
+        <v>2.533673536646796</v>
       </c>
       <c r="D1940" t="n">
         <v>-3.73536264914575</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.170898962618318</v>
+        <v>1.039172052674748</v>
       </c>
       <c r="F1940" t="n">
         <v>0.618183291951326</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.036310421761162</v>
+        <v>2.904583511817592</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.593938759991816</v>
+        <v>2.462211850048245</v>
       </c>
       <c r="D1941" t="n">
         <v>-3.729084446575901</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.101948557047708</v>
+        <v>0.9702216471041369</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6244614945211751</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.968615656704522</v>
+        <v>2.836888746760951</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.604111146423949</v>
+        <v>2.472384236480378</v>
       </c>
       <c r="D1942" t="n">
         <v>-3.669231827372178</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.136061991161329</v>
+        <v>1.004335081217758</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6244614945211751</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.978788043136654</v>
+        <v>2.847061133193083</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.599057416997809</v>
+        <v>2.467330507054238</v>
       </c>
       <c r="D1943" t="n">
         <v>-3.582988364345801</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.165505646945741</v>
+        <v>1.03377873700217</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6244614945211751</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.973734313710514</v>
+        <v>2.842007403766944</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.590833192442334</v>
+        <v>2.459106282498764</v>
       </c>
       <c r="D1944" t="n">
         <v>-3.628295183744781</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.139158694630674</v>
+        <v>1.007431784687103</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5836513315119443</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.941023991349501</v>
+        <v>2.80929708140593</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.591385065475436</v>
+        <v>2.459658155531865</v>
       </c>
       <c r="D1945" t="n">
         <v>-3.657328288447082</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.128097325782855</v>
+        <v>0.9963704158392843</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5836513315119443</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.941575864382603</v>
+        <v>2.809848954439032</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.520657757366802</v>
+        <v>2.388930847423231</v>
       </c>
       <c r="D1946" t="n">
         <v>-3.564517806996223</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.094494210254565</v>
+        <v>0.9627673003109938</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6764618129628036</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.926534845144484</v>
+        <v>2.794807935200913</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.522531233291402</v>
+        <v>2.390804323347832</v>
       </c>
       <c r="D1947" t="n">
         <v>-3.608907276325651</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.078611898447394</v>
+        <v>0.9468849885038235</v>
       </c>
       <c r="F1947" t="n">
         <v>0.6320723436333759</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.901774639471428</v>
+        <v>2.770047729527858</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.517606941803125</v>
+        <v>2.385880031859555</v>
       </c>
       <c r="D1948" t="n">
         <v>-3.588403582440153</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.081889084513316</v>
+        <v>0.9501621745697455</v>
       </c>
       <c r="F1948" t="n">
         <v>0.6525760375188733</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.90915256431445</v>
+        <v>2.777425654370879</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.523098237633793</v>
+        <v>2.391371327690222</v>
       </c>
       <c r="D1949" t="n">
         <v>-3.628327677022726</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.071410742510954</v>
+        <v>0.9396838325673837</v>
       </c>
       <c r="F1949" t="n">
         <v>0.6525760375188733</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.914643860145117</v>
+        <v>2.782916950201546</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.534595439402332</v>
+        <v>2.402868529458761</v>
       </c>
       <c r="D1950" t="n">
         <v>-3.656108074924079</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.071795785118952</v>
+        <v>0.9400688751753816</v>
       </c>
       <c r="F1950" t="n">
         <v>0.6247956396175203</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.909472823172844</v>
+        <v>2.777745913229273</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.372951159402985</v>
+        <v>2.241224249459414</v>
       </c>
       <c r="D1951" t="n">
         <v>-3.774488747654217</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8627992360275503</v>
+        <v>0.7310723260839795</v>
       </c>
       <c r="F1951" t="n">
         <v>0.5575777874665441</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.707497831882912</v>
+        <v>2.575770921939341</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.493100820122191</v>
+        <v>2.36137391017862</v>
       </c>
       <c r="D1952" t="n">
         <v>-3.883102826097548</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9395032653694235</v>
+        <v>0.8077763554258528</v>
       </c>
       <c r="F1952" t="n">
         <v>0.5575777874665441</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.827647492602118</v>
+        <v>2.695920582658547</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.507613846224514</v>
+        <v>2.375886936280943</v>
       </c>
       <c r="D1953" t="n">
         <v>-3.847693787849405</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9681799067710035</v>
+        <v>0.8364529968274328</v>
       </c>
       <c r="F1953" t="n">
         <v>0.5575777874665441</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.842160518704441</v>
+        <v>2.71043360876087</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.505033287566882</v>
+        <v>2.373306377623312</v>
       </c>
       <c r="D1954" t="n">
         <v>-3.856154956504867</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9622148806511879</v>
+        <v>0.8304879707076172</v>
       </c>
       <c r="F1954" t="n">
         <v>0.549116618811083</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.834503258853533</v>
+        <v>2.702776348909962</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.501762316412185</v>
+        <v>2.370035406468614</v>
       </c>
       <c r="D1955" t="n">
         <v>-3.6790386264697</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.029790441510557</v>
+        <v>0.8980635315669858</v>
       </c>
       <c r="F1955" t="n">
         <v>0.549116618811083</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.831232287698835</v>
+        <v>2.699505377755264</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.7413284487939</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.502445708174098</v>
+        <v>2.370718798230527</v>
       </c>
       <c r="D1956" t="n">
         <v>-3.724130871303246</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.012436935339051</v>
+        <v>0.8807100253954807</v>
       </c>
       <c r="F1956" t="n">
         <v>0.4872205756416932</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.794778053559114</v>
+        <v>2.663051143615543</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.496232683480512</v>
+        <v>2.364505773536941</v>
       </c>
       <c r="D1957" t="n">
         <v>-3.544755450064478</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.077974079140973</v>
+        <v>0.9462471691974021</v>
       </c>
       <c r="F1957" t="n">
         <v>0.6439973338124119</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.88263108376796</v>
+        <v>2.750904173824389</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982224</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.477040138812102</v>
+        <v>2.345313228868531</v>
       </c>
       <c r="D1958" t="n">
         <v>-3.589769663585085</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.04077584906432</v>
+        <v>0.9090489391207495</v>
       </c>
       <c r="F1958" t="n">
         <v>0.6136484384978073</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.845229201910787</v>
+        <v>2.713502291967216</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.482731701151048</v>
+        <v>2.351004791207477</v>
       </c>
       <c r="D1959" t="n">
         <v>-3.85677417385752</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9396656072942917</v>
+        <v>0.807938697350721</v>
       </c>
       <c r="F1959" t="n">
         <v>0.4192854004548587</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.734302941423963</v>
+        <v>2.602576031480393</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.481935623047549</v>
+        <v>2.350208713103978</v>
       </c>
       <c r="D1960" t="n">
         <v>-3.957971955294693</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.898390416615924</v>
+        <v>0.7666635066723533</v>
       </c>
       <c r="F1960" t="n">
         <v>0.3508765869095395</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.692461575193273</v>
+        <v>2.560734665249703</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.479535584601866</v>
+        <v>2.347808674658295</v>
       </c>
       <c r="D1961" t="n">
         <v>-3.95146098868038</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8985947648159658</v>
+        <v>0.7668678548723951</v>
       </c>
       <c r="F1961" t="n">
         <v>0.3508765869095395</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.69006153674759</v>
+        <v>2.558334626804019</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.476060303810111</v>
+        <v>2.34433339386654</v>
       </c>
       <c r="D1962" t="n">
         <v>-3.932422860973083</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9027347351071295</v>
+        <v>0.7710078251635588</v>
       </c>
       <c r="F1962" t="n">
         <v>0.2926929755783449</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.651676089157118</v>
+        <v>2.519949179213547</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.595354705444301</v>
+        <v>2.46362779550073</v>
       </c>
       <c r="D1963" t="n">
         <v>-3.984938663247903</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.001022815831392</v>
+        <v>0.8692959058878214</v>
       </c>
       <c r="F1963" t="n">
         <v>0.2926929755783449</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.770970490791308</v>
+        <v>2.639243580847737</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067862</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.596188034430435</v>
+        <v>2.464461124486864</v>
       </c>
       <c r="D1964" t="n">
         <v>-3.988346974682483</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.000492820243694</v>
+        <v>0.8687659103001228</v>
       </c>
       <c r="F1964" t="n">
         <v>0.3252095445877223</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.791313761183068</v>
+        <v>2.659586851239498</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.602196564827361</v>
+        <v>2.47046965488379</v>
       </c>
       <c r="D1965" t="n">
         <v>-3.968990838788636</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.014243804998158</v>
+        <v>0.8825168950545876</v>
       </c>
       <c r="F1965" t="n">
         <v>0.3252095445877223</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.797322291579994</v>
+        <v>2.665595381636424</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.50014678610456</v>
+        <v>2.368419876160989</v>
       </c>
       <c r="D1966" t="n">
         <v>-3.821247868553634</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9712912143693586</v>
+        <v>0.8395643044257879</v>
       </c>
       <c r="F1966" t="n">
         <v>0.4930169018226055</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.795956927198123</v>
+        <v>2.664230017254553</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.502940407636041</v>
+        <v>2.37121349769247</v>
       </c>
       <c r="D1967" t="n">
         <v>-3.905069089828332</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9405563473909604</v>
+        <v>0.8088294374473897</v>
       </c>
       <c r="F1967" t="n">
         <v>0.4930169018226055</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.798750548729604</v>
+        <v>2.667023638786034</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394725</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.503602756027699</v>
+        <v>2.371875846084129</v>
       </c>
       <c r="D1968" t="n">
         <v>-3.898916383775547</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9436797782037325</v>
+        <v>0.8119528682601618</v>
       </c>
       <c r="F1968" t="n">
         <v>0.4991696078753898</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.803104520752933</v>
+        <v>2.671377610809363</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.50268323276781</v>
+        <v>2.370956322824239</v>
       </c>
       <c r="D1969" t="n">
         <v>-3.915725681926049</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9360365356836422</v>
+        <v>0.8043096257400715</v>
       </c>
       <c r="F1969" t="n">
         <v>0.4823603097248881</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.792099418602743</v>
+        <v>2.660372508659172</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.569018786564631</v>
+        <v>2.43729187662106</v>
       </c>
       <c r="D1970" t="n">
         <v>-3.853427683149927</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.027291288990912</v>
+        <v>0.8955643790473411</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5276545739993301</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.885611530964229</v>
+        <v>2.753884621020658</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.371310788278758</v>
+        <v>2.239583878335187</v>
       </c>
       <c r="D1971" t="n">
         <v>-3.651637485484769</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9102993697711022</v>
+        <v>0.7785724598275314</v>
       </c>
       <c r="F1971" t="n">
         <v>0.7256727661684845</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.806714447979849</v>
+        <v>2.674987538036278</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.441601020600933</v>
+        <v>2.309874110657362</v>
       </c>
       <c r="D1972" t="n">
         <v>-3.702524198170964</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9602349170187994</v>
+        <v>0.8285080070752286</v>
       </c>
       <c r="F1972" t="n">
         <v>0.67478605348229</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.846472652690307</v>
+        <v>2.714745742746736</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.81906330031954</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.456228756716976</v>
+        <v>2.324501846773406</v>
       </c>
       <c r="D1973" t="n">
         <v>-3.615913455521156</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.009506950194766</v>
+        <v>0.8777800402511953</v>
       </c>
       <c r="F1973" t="n">
         <v>0.7534117846874483</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.908275827529446</v>
+        <v>2.776548917585875</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.83181903248938</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.454764737541648</v>
+        <v>2.323037827598077</v>
       </c>
       <c r="D1974" t="n">
         <v>-3.676122753526441</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9839592118173239</v>
+        <v>0.8522323018737532</v>
       </c>
       <c r="F1974" t="n">
         <v>0.6932024866821638</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.870686229550947</v>
+        <v>2.738959319607376</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.83641167239779</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.453256355581577</v>
+        <v>2.321529445638006</v>
       </c>
       <c r="D1975" t="n">
         <v>-3.626936104842089</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.002125489330993</v>
+        <v>0.8703985793874223</v>
       </c>
       <c r="F1975" t="n">
         <v>0.6932024866821638</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.869177847590875</v>
+        <v>2.737450937647305</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316245</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.453119223017013</v>
+        <v>2.321392313073442</v>
       </c>
       <c r="D1976" t="n">
         <v>-3.582562973203521</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.019737609421857</v>
+        <v>0.8880106994782859</v>
       </c>
       <c r="F1976" t="n">
         <v>0.7375756183207324</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.895664594009453</v>
+        <v>2.763937684065882</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.447513017155603</v>
+        <v>2.315786107212033</v>
       </c>
       <c r="D1977" t="n">
         <v>-3.54783165188502</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.028023932087847</v>
+        <v>0.8962970221442768</v>
       </c>
       <c r="F1977" t="n">
         <v>0.7375756183207324</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.890058388148043</v>
+        <v>2.758331478204473</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.453894774183408</v>
+        <v>2.322167864239837</v>
       </c>
       <c r="D1978" t="n">
         <v>-3.500175921323964</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.053467981340074</v>
+        <v>0.9217410713965037</v>
       </c>
       <c r="F1978" t="n">
         <v>0.785231348881788</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.925033583512481</v>
+        <v>2.79330667356891</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.458787147558133</v>
+        <v>2.327060237614562</v>
       </c>
       <c r="D1979" t="n">
         <v>-3.39965776282521</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.098567618114301</v>
+        <v>0.9668407081707304</v>
       </c>
       <c r="F1979" t="n">
         <v>0.8857495073805426</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.990236851986459</v>
+        <v>2.858509942042888</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.445541820034005</v>
+        <v>2.313814910090434</v>
       </c>
       <c r="D1980" t="n">
         <v>-3.383752433392857</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.091684422363114</v>
+        <v>0.9599575124195436</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8066368466713036</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.929523928036788</v>
+        <v>2.797797018093217</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.449639522644634</v>
+        <v>2.317912612701063</v>
       </c>
       <c r="D1981" t="n">
         <v>-3.338914031784459</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.113717485617102</v>
+        <v>0.9819905756735314</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8111802796161731</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.936347690414338</v>
+        <v>2.804620780470767</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.453800462275712</v>
+        <v>2.322073552332141</v>
       </c>
       <c r="D1982" t="n">
         <v>-3.358412488026467</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.110079042751377</v>
+        <v>0.9783521328078062</v>
       </c>
       <c r="F1982" t="n">
         <v>0.7630956383362688</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.911657845277473</v>
+        <v>2.779930935333903</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.459680064803549</v>
+        <v>2.327953154859978</v>
       </c>
       <c r="D1983" t="n">
         <v>-3.314209650940567</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.133639780113574</v>
+        <v>1.001912870170004</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8072984754221693</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.944059150056851</v>
+        <v>2.81233224011328</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.458090065272796</v>
+        <v>2.326363155329226</v>
       </c>
       <c r="D1984" t="n">
         <v>-3.321769316777614</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.129025914248003</v>
+        <v>0.9972990043044323</v>
       </c>
       <c r="F1984" t="n">
         <v>0.8621018794319886</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.97535119293199</v>
+        <v>2.843624282988419</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284878</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.509337830455836</v>
+        <v>2.377610920512265</v>
       </c>
       <c r="D1985" t="n">
         <v>-3.163477899238341</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.243590246446751</v>
+        <v>1.111863336503181</v>
       </c>
       <c r="F1985" t="n">
         <v>0.8621018794319886</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.026598958115029</v>
+        <v>2.894872048171459</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.507778535050089</v>
+        <v>2.376051625106518</v>
       </c>
       <c r="D1986" t="n">
         <v>-2.955835895603865</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.325087752494795</v>
+        <v>1.193360842551224</v>
       </c>
       <c r="F1986" t="n">
         <v>1.069743883066465</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.149624864889968</v>
+        <v>3.017897954946398</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.502726763288359</v>
+        <v>2.370999853344788</v>
       </c>
       <c r="D1987" t="n">
         <v>-2.904803802881337</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.340448817822076</v>
+        <v>1.208721907878506</v>
       </c>
       <c r="F1987" t="n">
         <v>1.120775975788993</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.175192348761755</v>
+        <v>3.043465438818184</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.519914167381064</v>
+        <v>2.388187257437493</v>
       </c>
       <c r="D1988" t="n">
         <v>-2.839579621754131</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.383725894365664</v>
+        <v>1.251998984422093</v>
       </c>
       <c r="F1988" t="n">
         <v>1.186000156916198</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.231514261530783</v>
+        <v>3.099787351587213</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.515875139680344</v>
+        <v>2.384148229736774</v>
       </c>
       <c r="D1989" t="n">
         <v>-2.802152601682998</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.394657674693397</v>
+        <v>1.262930764749827</v>
       </c>
       <c r="F1989" t="n">
         <v>1.19125169494538</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.230626156647573</v>
+        <v>3.098899246704002</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.517131932011585</v>
+        <v>2.385405022068014</v>
       </c>
       <c r="D1990" t="n">
         <v>-2.800794616709452</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.396457661014056</v>
+        <v>1.264730751070485</v>
       </c>
       <c r="F1990" t="n">
         <v>1.265589820483199</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.276485824301504</v>
+        <v>3.144758914357934</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.677689703032796</v>
+        <v>2.545962793089225</v>
       </c>
       <c r="D1991" t="n">
         <v>-2.772381353609568</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.56838073727522</v>
+        <v>1.436653827331649</v>
       </c>
       <c r="F1991" t="n">
         <v>1.20661425773677</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.401658257674858</v>
+        <v>3.269931347731287</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.797802612250613</v>
+        <v>2.666075702307042</v>
       </c>
       <c r="D1992" t="n">
         <v>-2.697599092584556</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.718406550903042</v>
+        <v>1.586679640959472</v>
       </c>
       <c r="F1992" t="n">
         <v>1.281396518761783</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.566640523507683</v>
+        <v>3.434913613564112</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.789510588264472</v>
+        <v>2.657783678320901</v>
       </c>
       <c r="D1993" t="n">
         <v>-2.671515008320748</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.720548160622425</v>
+        <v>1.588821250678854</v>
       </c>
       <c r="F1993" t="n">
         <v>1.281396518761783</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.558348499521542</v>
+        <v>3.426621589577971</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.787703783848251</v>
+        <v>2.655976873904681</v>
       </c>
       <c r="D1994" t="n">
         <v>-2.583637095211627</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.753892521449852</v>
+        <v>1.622165611506282</v>
       </c>
       <c r="F1994" t="n">
         <v>1.397322161185134</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.626097080559332</v>
+        <v>3.494370170615761</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.805258189575043</v>
+        <v>2.673531279631472</v>
       </c>
       <c r="D1995" t="n">
         <v>-2.574744633818344</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.775003911733957</v>
+        <v>1.643277001790386</v>
       </c>
       <c r="F1995" t="n">
         <v>1.397322161185134</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.643651486286123</v>
+        <v>3.511924576342552</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.797113236979627</v>
+        <v>2.665386327036056</v>
       </c>
       <c r="D1996" t="n">
         <v>-2.743220750788222</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.69946851235059</v>
+        <v>1.567741602407019</v>
       </c>
       <c r="F1996" t="n">
         <v>1.369374325468553</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.618737832260758</v>
+        <v>3.487010922317188</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.778382934167488</v>
+        <v>2.646656024223918</v>
       </c>
       <c r="D1997" t="n">
         <v>-2.296964558158782</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.859240686590228</v>
+        <v>1.727513776646657</v>
       </c>
       <c r="F1997" t="n">
         <v>1.27465565579892</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.543176327646841</v>
+        <v>3.41144941770327</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.769046956664393</v>
+        <v>2.637320046720822</v>
       </c>
       <c r="D1998" t="n">
         <v>-2.27424345447563</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.858993150560393</v>
+        <v>1.727266240616822</v>
       </c>
       <c r="F1998" t="n">
         <v>1.27465565579892</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.533840350143745</v>
+        <v>3.402113440200174</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.927953082515562</v>
+        <v>2.796226172571991</v>
       </c>
       <c r="D1999" t="n">
         <v>-2.403445267769672</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.966218551093945</v>
+        <v>1.834491641150374</v>
       </c>
       <c r="F1999" t="n">
         <v>1.145453842504878</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.615225388018489</v>
+        <v>3.483498478074918</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.965030905009209</v>
+        <v>2.833303995065638</v>
       </c>
       <c r="D2000" t="n">
         <v>-2.429319666243698</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.992946614197981</v>
+        <v>1.861219704254411</v>
       </c>
       <c r="F2000" t="n">
         <v>1.190365451216619</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.67925017573918</v>
+        <v>3.54752326579561</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.961706260998754</v>
+        <v>2.829979351055183</v>
       </c>
       <c r="D2001" t="n">
         <v>-2.422264976028524</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.992443846273596</v>
+        <v>1.860716936330025</v>
       </c>
       <c r="F2001" t="n">
         <v>1.197420141431793</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.68015834585783</v>
+        <v>3.548431435914259</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.971712414643495</v>
+        <v>2.839985504699925</v>
       </c>
       <c r="D2002" t="n">
         <v>-2.395313751702036</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.013230489648933</v>
+        <v>1.881503579705362</v>
       </c>
       <c r="F2002" t="n">
         <v>1.212300487459512</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.699092707119203</v>
+        <v>3.567365797175632</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.155815546788455</v>
+        <v>3.024088636844884</v>
       </c>
       <c r="D2003" t="n">
         <v>-2.416857979532824</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.188715930661578</v>
+        <v>2.056989020718007</v>
       </c>
       <c r="F2003" t="n">
         <v>1.212300487459512</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.883195839264162</v>
+        <v>3.751468929320592</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.147932241691448</v>
+        <v>3.016205331747877</v>
       </c>
       <c r="D2004" t="n">
         <v>-2.439266097337696</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.171869378442622</v>
+        <v>2.040142468499051</v>
       </c>
       <c r="F2004" t="n">
         <v>1.212300487459512</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.875312534167155</v>
+        <v>3.743585624223585</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.149986241241086</v>
+        <v>3.018259331297515</v>
       </c>
       <c r="D2005" t="n">
         <v>-2.467490332915296</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.162633683761219</v>
+        <v>2.030906773817649</v>
       </c>
       <c r="F2005" t="n">
         <v>1.230277239910821</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.888152585187578</v>
+        <v>3.756425675244008</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.206239958962933</v>
+        <v>3.074513049019362</v>
       </c>
       <c r="D2006" t="n">
         <v>-2.476931258803826</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.215111031127655</v>
+        <v>2.083384121184084</v>
       </c>
       <c r="F2006" t="n">
         <v>1.352704357454212</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.01786257343546</v>
+        <v>3.886135663491889</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.209131053508234</v>
+        <v>3.077404143564663</v>
       </c>
       <c r="D2007" t="n">
         <v>-2.5658078899723</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.182451473205566</v>
+        <v>2.050724563261995</v>
       </c>
       <c r="F2007" t="n">
         <v>1.263827726285738</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.967427689279677</v>
+        <v>3.835700779336106</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.207242866402009</v>
+        <v>3.075515956458438</v>
       </c>
       <c r="D2008" t="n">
         <v>-2.642137867573206</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.150031295058978</v>
+        <v>2.018304385115408</v>
       </c>
       <c r="F2008" t="n">
         <v>1.263827726285738</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.965539502173452</v>
+        <v>3.833812592229881</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.202063096004871</v>
+        <v>3.0703361860613</v>
       </c>
       <c r="D2009" t="n">
         <v>-2.797094652973335</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.082868810501789</v>
+        <v>1.951141900558218</v>
       </c>
       <c r="F2009" t="n">
         <v>1.108870940885609</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.867385660536237</v>
+        <v>3.735658750592666</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.200497106215023</v>
+        <v>3.068770196271453</v>
       </c>
       <c r="D2010" t="n">
         <v>-2.95866307850059</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.016675450501039</v>
+        <v>1.884948540557469</v>
       </c>
       <c r="F2010" t="n">
         <v>0.9820880170877296</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.789749916467661</v>
+        <v>3.658023006524091</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.213570513080942</v>
+        <v>3.081843603137371</v>
       </c>
       <c r="D2011" t="n">
         <v>-3.06696374037071</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.98642859261891</v>
+        <v>1.85470168267534</v>
       </c>
       <c r="F2011" t="n">
         <v>0.9820880170877296</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.80282332333358</v>
+        <v>3.671096413390009</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.205575709863882</v>
+        <v>3.073848799920311</v>
       </c>
       <c r="D2012" t="n">
         <v>-3.084767712091454</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.971312200713553</v>
+        <v>1.839585290769982</v>
       </c>
       <c r="F2012" t="n">
         <v>0.9115533941825285</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.752507746373399</v>
+        <v>3.620780836429828</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.204099750990884</v>
+        <v>3.072372841047313</v>
       </c>
       <c r="D2013" t="n">
         <v>-3.112668499200927</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.958675926996765</v>
+        <v>1.826949017053195</v>
       </c>
       <c r="F2013" t="n">
         <v>0.8769564700395936</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.73027363301464</v>
+        <v>3.598546723071069</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.200864194968083</v>
+        <v>3.069137285024512</v>
       </c>
       <c r="D2014" t="n">
         <v>-3.23519460190382</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.906429929892806</v>
+        <v>1.774703019949236</v>
       </c>
       <c r="F2014" t="n">
         <v>0.7544303673366998</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.653522415370103</v>
+        <v>3.521795505426532</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.267570154558586</v>
+        <v>3.135843244615016</v>
       </c>
       <c r="D2015" t="n">
         <v>-3.465709098089409</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.880930091009075</v>
+        <v>1.749203181065504</v>
       </c>
       <c r="F2015" t="n">
         <v>0.523915871151111</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.581919677249253</v>
+        <v>3.450192767305682</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.407881873560433</v>
+        <v>3.276154963616863</v>
       </c>
       <c r="D2016" t="n">
         <v>-3.814454183313853</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.881743775921144</v>
+        <v>1.750016865977574</v>
       </c>
       <c r="F2016" t="n">
         <v>0.4151679172322132</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.656982623899762</v>
+        <v>3.525255713956191</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.476862142706073</v>
+        <v>3.345135232762503</v>
       </c>
       <c r="D2017" t="n">
         <v>-3.968440601089993</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.889129477956328</v>
+        <v>1.757402568012757</v>
       </c>
       <c r="F2017" t="n">
         <v>0.4151679172322132</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.725962893045402</v>
+        <v>3.594235983101831</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.462913344826194</v>
+        <v>3.331186434882623</v>
       </c>
       <c r="D2018" t="n">
         <v>-4.173040035953002</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.793340906131246</v>
+        <v>1.661613996187675</v>
       </c>
       <c r="F2018" t="n">
         <v>0.4151679172322132</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.712014095165522</v>
+        <v>3.580287185221952</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.474783833881608</v>
+        <v>3.343056923938037</v>
       </c>
       <c r="D2019" t="n">
         <v>-4.425515189960726</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.70422133358357</v>
+        <v>1.572494423639999</v>
       </c>
       <c r="F2019" t="n">
         <v>0.4151679172322132</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.723884584220936</v>
+        <v>3.592157674277366</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.475994368400552</v>
+        <v>3.344267458456981</v>
       </c>
       <c r="D2020" t="n">
         <v>-4.718410946440138</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.588273565510748</v>
+        <v>1.456546655567178</v>
       </c>
       <c r="F2020" t="n">
         <v>0.4151679172322132</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.72509511873988</v>
+        <v>3.593368208796309</v>
       </c>
     </row>
     <row r="2021">
@@ -48031,19 +48031,19 @@
         <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.480116110627873</v>
+        <v>3.348389200684303</v>
       </c>
       <c r="D2021" t="n">
         <v>-4.905075074574946</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.517729656484147</v>
+        <v>1.386002746540576</v>
       </c>
       <c r="F2021" t="n">
         <v>0.3884289464076534</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.713173478472465</v>
+        <v>3.581446568528895</v>
       </c>
     </row>
     <row r="2022">
@@ -48054,19 +48054,19 @@
         <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.475193963364063</v>
+        <v>3.343467053420492</v>
       </c>
       <c r="D2022" t="n">
         <v>-5.051095761488908</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.454399234454751</v>
+        <v>1.32267232451118</v>
       </c>
       <c r="F2022" t="n">
         <v>0.3793458546137964</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.702801476132341</v>
+        <v>3.57107456618877</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.637398020063107</v>
+        <v>3.505671110119536</v>
       </c>
       <c r="D2023" t="n">
         <v>-5.142809770598493</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.579917687509961</v>
+        <v>1.448190777566391</v>
       </c>
       <c r="F2023" t="n">
         <v>0.3793458546137964</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.865005532831385</v>
+        <v>3.733278622887814</v>
       </c>
     </row>
     <row r="2024">
@@ -48100,19 +48100,19 @@
         <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.632244658026921</v>
+        <v>3.50051774808335</v>
       </c>
       <c r="D2024" t="n">
         <v>-5.174461429658463</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.562103661849788</v>
+        <v>1.430376751906217</v>
       </c>
       <c r="F2024" t="n">
         <v>0.3741773973693562</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.856751096448535</v>
+        <v>3.725024186504964</v>
       </c>
     </row>
     <row r="2025">
@@ -48123,19 +48123,19 @@
         <v>3.750044015868142</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.642474075595412</v>
+        <v>3.510747165651841</v>
       </c>
       <c r="D2025" t="n">
         <v>-5.243527484231399</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.544706657589105</v>
+        <v>1.412979747645534</v>
       </c>
       <c r="F2025" t="n">
         <v>0.3118065198757461</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.82955798752086</v>
+        <v>3.697831077577289</v>
       </c>
     </row>
     <row r="2026">
@@ -48146,19 +48146,19 @@
         <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.651399714051315</v>
+        <v>3.519672804107744</v>
       </c>
       <c r="D2026" t="n">
         <v>-5.345503606479807</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.512841847145644</v>
+        <v>1.381114937202073</v>
       </c>
       <c r="F2026" t="n">
         <v>0.2098303976273386</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.777297952627718</v>
+        <v>3.645571042684147</v>
       </c>
     </row>
     <row r="2027">
@@ -48169,19 +48169,19 @@
         <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.64355260129549</v>
+        <v>3.511825691351919</v>
       </c>
       <c r="D2027" t="n">
         <v>-5.235497323002585</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.548997247780708</v>
+        <v>1.417270337837137</v>
       </c>
       <c r="F2027" t="n">
         <v>0.2330349695446138</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.783373583022259</v>
+        <v>3.651646673078688</v>
       </c>
     </row>
     <row r="2028">
@@ -48192,19 +48192,19 @@
         <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.647802612017464</v>
+        <v>3.516075702073894</v>
       </c>
       <c r="D2028" t="n">
         <v>-5.092437747261659</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.610471088799053</v>
+        <v>1.478744178855482</v>
       </c>
       <c r="F2028" t="n">
         <v>0.2410483961345931</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.79243164969822</v>
+        <v>3.660704739754649</v>
       </c>
     </row>
     <row r="2029">
@@ -48215,19 +48215,19 @@
         <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.6550634949</v>
+        <v>3.52333658495643</v>
       </c>
       <c r="D2029" t="n">
         <v>-4.790991021789822</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.738310661870324</v>
+        <v>1.606583751926753</v>
       </c>
       <c r="F2029" t="n">
         <v>0.5424951216064303</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.980560567863859</v>
+        <v>3.848833657920288</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.656034672652711</v>
+        <v>3.52430776270914</v>
       </c>
       <c r="D2030" t="n">
         <v>-4.815581266025005</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.729445741928961</v>
+        <v>1.59771883198539</v>
       </c>
       <c r="F2030" t="n">
         <v>0.5424951216064303</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.98153174561657</v>
+        <v>3.849804835672999</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.656877577032466</v>
+        <v>3.525150667088896</v>
       </c>
       <c r="D2031" t="n">
         <v>-4.764542890018485</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.750703996711324</v>
+        <v>1.618977086767754</v>
       </c>
       <c r="F2031" t="n">
         <v>0.5424951216064303</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.982374649996325</v>
+        <v>3.850647740052754</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.675915675906612</v>
+        <v>3.544188765963041</v>
       </c>
       <c r="D2032" t="n">
         <v>-4.723403595151854</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.786197813532122</v>
+        <v>1.654470903588551</v>
       </c>
       <c r="F2032" t="n">
         <v>0.5836344164730611</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.026096325790449</v>
+        <v>3.894369415846878</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.825752932700475</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.492099672030546</v>
+        <v>3.360372762086976</v>
       </c>
       <c r="D2033" t="n">
         <v>-4.626768683133214</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.641035774463513</v>
+        <v>1.509308864519942</v>
       </c>
       <c r="F2033" t="n">
         <v>0.6802693284917011</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.900261269125567</v>
+        <v>3.768534359181996</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077637</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.495601716104511</v>
+        <v>3.36387480616094</v>
       </c>
       <c r="D2034" t="n">
         <v>-4.557730672184746</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.672153022916864</v>
+        <v>1.540426112973293</v>
       </c>
       <c r="F2034" t="n">
         <v>0.7493073394401691</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.945186119768612</v>
+        <v>3.813459209825042</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.480028535180593</v>
+        <v>3.348301625237022</v>
       </c>
       <c r="D2035" t="n">
         <v>-4.393234337993785</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.722378375669331</v>
+        <v>1.59065146572576</v>
       </c>
       <c r="F2035" t="n">
         <v>0.913803673631131</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.028310739359272</v>
+        <v>3.896583829415701</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.479216245617023</v>
+        <v>3.347489335673452</v>
       </c>
       <c r="D2036" t="n">
         <v>-4.316135736451912</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.75240552672251</v>
+        <v>1.620678616778939</v>
       </c>
       <c r="F2036" t="n">
         <v>0.913803673631131</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.027498449795702</v>
+        <v>3.895771539852131</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.489085024742095</v>
+        <v>3.357358114798525</v>
       </c>
       <c r="D2037" t="n">
         <v>-4.326520931341801</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.758120227891627</v>
+        <v>1.626393317948056</v>
       </c>
       <c r="F2037" t="n">
         <v>0.9034184787412417</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.03113611198684</v>
+        <v>3.89940920204327</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.55992203051852</v>
+        <v>3.42819512057495</v>
       </c>
       <c r="D2038" t="n">
         <v>-4.345109090064026</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.821521970179162</v>
+        <v>1.689795060235591</v>
       </c>
       <c r="F2038" t="n">
         <v>0.8848303200190164</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.09082022252993</v>
+        <v>3.95909331258636</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496554</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.556791041336819</v>
+        <v>3.425064131393248</v>
       </c>
       <c r="D2039" t="n">
         <v>-4.345407636760062</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.818271562319046</v>
+        <v>1.686544652375475</v>
       </c>
       <c r="F2039" t="n">
         <v>0.8845317733229805</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.087510105330607</v>
+        <v>3.955783195387037</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.56132193627621</v>
+        <v>3.42959502633264</v>
       </c>
       <c r="D2040" t="n">
         <v>-4.244584503069635</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.863131710734609</v>
+        <v>1.731404800791038</v>
       </c>
       <c r="F2040" t="n">
         <v>0.8969959888073343</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.099519529560611</v>
+        <v>3.967792619617041</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.561451189754754</v>
+        <v>3.429724279811183</v>
       </c>
       <c r="D2041" t="n">
         <v>-4.053803142317227</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.939573508514115</v>
+        <v>1.807846598570544</v>
       </c>
       <c r="F2041" t="n">
         <v>1.087777349559742</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.214117599490599</v>
+        <v>4.082390689547028</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.54128803549235</v>
+        <v>3.409561125548779</v>
       </c>
       <c r="D2042" t="n">
         <v>-3.946839784467805</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.96219569739148</v>
+        <v>1.830468787447909</v>
       </c>
       <c r="F2042" t="n">
         <v>1.146241957519543</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.229033210004077</v>
+        <v>4.097306300060506</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.576254972104409</v>
+        <v>3.444528062160838</v>
       </c>
       <c r="D2043" t="n">
         <v>-3.891509196566043</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.019294869164243</v>
+        <v>1.887567959220673</v>
       </c>
       <c r="F2043" t="n">
         <v>1.201572545421305</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.297198499357192</v>
+        <v>4.165471589413621</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.569941540005846</v>
+        <v>3.438214630062276</v>
       </c>
       <c r="D2044" t="n">
         <v>-3.87945506965308</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.017803087830866</v>
+        <v>1.886076177887295</v>
       </c>
       <c r="F2044" t="n">
         <v>1.213626672334268</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.298117543406407</v>
+        <v>4.166390633462837</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.571822170189982</v>
+        <v>3.440095260246411</v>
       </c>
       <c r="D2045" t="n">
         <v>-3.920610189221301</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.003221670187714</v>
+        <v>1.871494760244143</v>
       </c>
       <c r="F2045" t="n">
         <v>1.172471552766047</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.275305101849611</v>
+        <v>4.14357819190604</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.584673196067865</v>
+        <v>3.452946286124294</v>
       </c>
       <c r="D2046" t="n">
         <v>-3.852561626529771</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.043292121142208</v>
+        <v>1.911565211198637</v>
       </c>
       <c r="F2046" t="n">
         <v>1.240520115457577</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.328985265342411</v>
+        <v>4.197258355398841</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.645256780013423</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.604875866241459</v>
+        <v>3.473148956297888</v>
       </c>
       <c r="D2047" t="n">
         <v>-4.084162019699273</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.970854634048002</v>
+        <v>1.839127724104431</v>
       </c>
       <c r="F2047" t="n">
         <v>1.240520115457577</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.349187935516005</v>
+        <v>4.217461025572435</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.588482102308341</v>
+        <v>3.45675519236477</v>
       </c>
       <c r="D2048" t="n">
         <v>-4.134213565228492</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.934440251903196</v>
+        <v>1.802713341959625</v>
       </c>
       <c r="F2048" t="n">
         <v>1.240520115457577</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.332794171582887</v>
+        <v>4.201067261639317</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670048702800098</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.548734015901807</v>
+        <v>3.417007105958237</v>
       </c>
       <c r="D2049" t="n">
         <v>-4.309320397804937</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.824649432466085</v>
+        <v>1.692922522522514</v>
       </c>
       <c r="F2049" t="n">
         <v>1.240520115457577</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.293046085176353</v>
+        <v>4.161319175232784</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.74557314866085</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.555756634898747</v>
+        <v>3.424029724955177</v>
       </c>
       <c r="D2050" t="n">
         <v>-4.113220244374414</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.910112112835234</v>
+        <v>1.778385202891663</v>
       </c>
       <c r="F2050" t="n">
         <v>1.4366202688881</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.417728796231607</v>
+        <v>4.286001886288037</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730570473395087</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.654927634471652</v>
+        <v>3.523200724528081</v>
       </c>
       <c r="D2051" t="n">
         <v>-3.96019485226113</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.070493269253452</v>
+        <v>1.938766359309881</v>
       </c>
       <c r="F2051" t="n">
         <v>1.589645661001384</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.608715031072482</v>
+        <v>4.476988121128912</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741278332791149</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.842393859379944</v>
+        <v>3.710666949436374</v>
       </c>
       <c r="D2052" t="n">
         <v>-3.9885021661344</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.246636568612437</v>
+        <v>2.114909658668866</v>
       </c>
       <c r="F2052" t="n">
         <v>1.589645661001384</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.796181255980775</v>
+        <v>4.664454346037204</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.811796810734027</v>
+        <v>3.680069900790456</v>
       </c>
       <c r="D2053" t="n">
         <v>-4.155095391247922</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.14940222992111</v>
+        <v>2.01767531997754</v>
       </c>
       <c r="F2053" t="n">
         <v>1.423052435887861</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.665628272266744</v>
+        <v>4.533901362323173</v>
       </c>
     </row>
     <row r="2054">
@@ -48790,19 +48790,19 @@
         <v>3.708182519285647</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.815473213395745</v>
+        <v>3.683746303452174</v>
       </c>
       <c r="D2054" t="n">
         <v>-4.132059597886356</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.162292949927454</v>
+        <v>2.030566039983884</v>
       </c>
       <c r="F2054" t="n">
         <v>1.423052435887861</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.669304674928462</v>
+        <v>4.537577764984891</v>
       </c>
     </row>
     <row r="2055">
@@ -48813,19 +48813,19 @@
         <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.81309126851924</v>
+        <v>3.681364358575669</v>
       </c>
       <c r="D2055" t="n">
         <v>-4.10281361743066</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.171609397233228</v>
+        <v>2.039882487289657</v>
       </c>
       <c r="F2055" t="n">
         <v>1.423052435887861</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.666922730051957</v>
+        <v>4.535195820108386</v>
       </c>
     </row>
     <row r="2056">
@@ -48836,19 +48836,19 @@
         <v>3.69940464225637</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.810384507676875</v>
+        <v>3.678657597733304</v>
       </c>
       <c r="D2056" t="n">
         <v>-4.209739165308511</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.126132417239723</v>
+        <v>1.994405507296152</v>
       </c>
       <c r="F2056" t="n">
         <v>1.31612688801001</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.600060640482882</v>
+        <v>4.468333730539311</v>
       </c>
     </row>
     <row r="2057">
@@ -48859,19 +48859,19 @@
         <v>3.689942600701</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.811813309820109</v>
+        <v>3.680086399876539</v>
       </c>
       <c r="D2057" t="n">
         <v>-4.35475772381576</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.069553795980058</v>
+        <v>1.937826886036487</v>
       </c>
       <c r="F2057" t="n">
         <v>1.171108329502762</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.514478307521767</v>
+        <v>4.382751397578196</v>
       </c>
     </row>
     <row r="2058">
@@ -48882,19 +48882,19 @@
         <v>3.711852429687012</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.911744549077862</v>
+        <v>3.780017639134292</v>
       </c>
       <c r="D2058" t="n">
         <v>-4.473099489600477</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.122148328923924</v>
+        <v>1.990421418980353</v>
       </c>
       <c r="F2058" t="n">
         <v>1.181794368065652</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.620821169917254</v>
+        <v>4.489094259973683</v>
       </c>
     </row>
     <row r="2059">
@@ -48905,19 +48905,19 @@
         <v>3.714879051790802</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.909530246203802</v>
+        <v>3.777803336260231</v>
       </c>
       <c r="D2059" t="n">
         <v>-4.524509911921185</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.099369857121579</v>
+        <v>1.967642947178009</v>
       </c>
       <c r="F2059" t="n">
         <v>1.181794368065652</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.618606867043193</v>
+        <v>4.486879957099622</v>
       </c>
     </row>
     <row r="2060">
@@ -48928,19 +48928,19 @@
         <v>3.704757949437329</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.909433374278091</v>
+        <v>3.77770646433452</v>
       </c>
       <c r="D2060" t="n">
         <v>-4.603929363128937</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.067505204712768</v>
+        <v>1.935778294769197</v>
       </c>
       <c r="F2060" t="n">
         <v>1.181794368065652</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.618509995117482</v>
+        <v>4.486783085173911</v>
       </c>
     </row>
     <row r="2061">
@@ -48951,19 +48951,19 @@
         <v>3.736804952298396</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.909427267836134</v>
+        <v>3.777700357892563</v>
       </c>
       <c r="D2061" t="n">
         <v>-4.699392361046154</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.029313899103924</v>
+        <v>1.897586989160353</v>
       </c>
       <c r="F2061" t="n">
         <v>1.181794368065652</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.618503888675525</v>
+        <v>4.486776978731954</v>
       </c>
     </row>
     <row r="2062">
@@ -48974,19 +48974,19 @@
         <v>3.715372960217998</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.907523664398744</v>
+        <v>3.775796754455174</v>
       </c>
       <c r="D2062" t="n">
         <v>-4.635016450195439</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.053160660006821</v>
+        <v>1.92143375006325</v>
       </c>
       <c r="F2062" t="n">
         <v>1.246170278916367</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.655225831748565</v>
+        <v>4.523498921804994</v>
       </c>
     </row>
     <row r="2063">
@@ -48997,19 +48997,19 @@
         <v>3.736089413353533</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.913257482146471</v>
+        <v>3.7815305722029</v>
       </c>
       <c r="D2063" t="n">
         <v>-4.690385612327633</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.036746812901669</v>
+        <v>1.905019902958099</v>
       </c>
       <c r="F2063" t="n">
         <v>1.246170278916367</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.660959649496291</v>
+        <v>4.529232739552721</v>
       </c>
     </row>
     <row r="2064">
@@ -49020,19 +49020,19 @@
         <v>3.736822870113277</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.912795845489403</v>
+        <v>3.781068935545833</v>
       </c>
       <c r="D2064" t="n">
         <v>-4.708604079325242</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.028997789445559</v>
+        <v>1.897270879501988</v>
       </c>
       <c r="F2064" t="n">
         <v>1.221063841660525</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.645434150485719</v>
+        <v>4.513707240542148</v>
       </c>
     </row>
     <row r="2065">
@@ -49043,19 +49043,19 @@
         <v>3.790272500113685</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.932670238339722</v>
+        <v>3.800943328396151</v>
       </c>
       <c r="D2065" t="n">
         <v>-4.620397245177664</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.084154915954909</v>
+        <v>1.952428006011338</v>
       </c>
       <c r="F2065" t="n">
         <v>1.221063841660525</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.665308543336037</v>
+        <v>4.533581633392466</v>
       </c>
     </row>
     <row r="2066">
@@ -49066,19 +49066,19 @@
         <v>3.794486844016439</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.91637093886445</v>
+        <v>3.784644028920879</v>
       </c>
       <c r="D2066" t="n">
         <v>-4.514362249972354</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.11026961456176</v>
+        <v>1.97854270461819</v>
       </c>
       <c r="F2066" t="n">
         <v>1.221063841660525</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.649009243860765</v>
+        <v>4.517282333917194</v>
       </c>
     </row>
     <row r="2067">
@@ -49089,19 +49089,19 @@
         <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.918801888328495</v>
+        <v>3.787074978384925</v>
       </c>
       <c r="D2067" t="n">
         <v>-4.331150586839259</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.185985229279044</v>
+        <v>2.054258319335474</v>
       </c>
       <c r="F2067" t="n">
         <v>1.221063841660525</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.65144019332481</v>
+        <v>4.519713283381241</v>
       </c>
     </row>
     <row r="2068">
@@ -49112,19 +49112,19 @@
         <v>3.776846557863552</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.884593074176385</v>
+        <v>3.752866164232815</v>
       </c>
       <c r="D2068" t="n">
         <v>-4.259429139825408</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.180464993932474</v>
+        <v>2.048738083988904</v>
       </c>
       <c r="F2068" t="n">
         <v>1.292785288674375</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.660264247381011</v>
+        <v>4.528537337437441</v>
       </c>
     </row>
     <row r="2069">
@@ -49135,19 +49135,19 @@
         <v>3.723789705394112</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.831508820097557</v>
+        <v>3.699781910153987</v>
       </c>
       <c r="D2069" t="n">
         <v>-4.237056114217702</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.136329950096728</v>
+        <v>2.004603040153158</v>
       </c>
       <c r="F2069" t="n">
         <v>1.304041039787277</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.613933443969923</v>
+        <v>4.482206534026353</v>
       </c>
     </row>
     <row r="2070">
@@ -49158,19 +49158,19 @@
         <v>3.715607446456729</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.016707024982912</v>
+        <v>3.884980115039342</v>
       </c>
       <c r="D2070" t="n">
         <v>-4.270072410128447</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.308321636617785</v>
+        <v>2.176594726674216</v>
       </c>
       <c r="F2070" t="n">
         <v>1.234603663120525</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.757469222855227</v>
+        <v>4.625742312911657</v>
       </c>
     </row>
     <row r="2071">
@@ -49181,19 +49181,19 @@
         <v>3.713762536883675</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.008628250811161</v>
+        <v>3.876901340867592</v>
       </c>
       <c r="D2071" t="n">
         <v>-4.258544774478838</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.304853916705878</v>
+        <v>2.173127006762309</v>
       </c>
       <c r="F2071" t="n">
         <v>1.293604321321888</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.784790843604294</v>
+        <v>4.653063933660724</v>
       </c>
     </row>
     <row r="2072">
@@ -49204,19 +49204,19 @@
         <v>3.717150699236296</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.01229636333295</v>
+        <v>3.88056945338938</v>
       </c>
       <c r="D2072" t="n">
         <v>-4.355886275821207</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.269585428690719</v>
+        <v>2.13785851874715</v>
       </c>
       <c r="F2072" t="n">
         <v>1.249184139156399</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.761806846826789</v>
+        <v>4.63007993688322</v>
       </c>
     </row>
     <row r="2073">
@@ -49227,19 +49227,19 @@
         <v>3.705201079427682</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.013547445525788</v>
+        <v>3.881820535582218</v>
       </c>
       <c r="D2073" t="n">
         <v>-4.441742305161173</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.236494099147571</v>
+        <v>2.104767189204001</v>
       </c>
       <c r="F2073" t="n">
         <v>1.206808069930264</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.737632287483946</v>
+        <v>4.605905377540378</v>
       </c>
     </row>
     <row r="2074">
@@ -49250,19 +49250,19 @@
         <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.99596664734629</v>
+        <v>3.864239737402721</v>
       </c>
       <c r="D2074" t="n">
         <v>-4.450579102577293</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.215378582001625</v>
+        <v>2.083651672058056</v>
       </c>
       <c r="F2074" t="n">
         <v>1.199365897288914</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.715586185719638</v>
+        <v>4.583859275776069</v>
       </c>
     </row>
     <row r="2075">
@@ -49273,19 +49273,19 @@
         <v>3.715544411667453</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.006131158391339</v>
+        <v>3.87440424844777</v>
       </c>
       <c r="D2075" t="n">
         <v>-4.541961665142751</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.188990068020491</v>
+        <v>2.057263158076922</v>
       </c>
       <c r="F2075" t="n">
         <v>1.162801012569569</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.70381176593308</v>
+        <v>4.572084855989512</v>
       </c>
     </row>
     <row r="2076">
@@ -49296,19 +49296,19 @@
         <v>3.673978374889189</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.108259416215606</v>
+        <v>3.976532506272038</v>
       </c>
       <c r="D2076" t="n">
         <v>-4.530254947155745</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.295801013039561</v>
+        <v>2.164074103095992</v>
       </c>
       <c r="F2076" t="n">
         <v>1.174507730556575</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.812964054549552</v>
+        <v>4.681237144605984</v>
       </c>
     </row>
     <row r="2077">
@@ -49319,19 +49319,19 @@
         <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.111291754947011</v>
+        <v>3.979564845003443</v>
       </c>
       <c r="D2077" t="n">
         <v>-4.601167020898023</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.270468522274054</v>
+        <v>2.138741612330486</v>
       </c>
       <c r="F2077" t="n">
         <v>1.174507730556575</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.815996393280956</v>
+        <v>4.684269483337388</v>
       </c>
     </row>
     <row r="2078">
@@ -49342,19 +49342,19 @@
         <v>3.672895177452571</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.324196588225069</v>
+        <v>4.192469678281501</v>
       </c>
       <c r="D2078" t="n">
         <v>-4.611483119064375</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.479246916285571</v>
+        <v>2.347520006342003</v>
       </c>
       <c r="F2078" t="n">
         <v>1.174507730556575</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.028901226559015</v>
+        <v>4.897174316615446</v>
       </c>
     </row>
     <row r="2079">
@@ -49365,19 +49365,19 @@
         <v>3.623960959762284</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.323375255137159</v>
+        <v>4.191648345193591</v>
       </c>
       <c r="D2079" t="n">
         <v>-4.611389151047002</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.47846317040461</v>
+        <v>2.346736260461042</v>
       </c>
       <c r="F2079" t="n">
         <v>1.174877591903893</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.028301810279495</v>
+        <v>4.896574900335927</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.634813277125768</v>
+        <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.317607241081513</v>
+        <v>4.185880331137945</v>
       </c>
       <c r="D2080" t="n">
         <v>-4.759755378703147</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.413348665286506</v>
+        <v>2.281621755342938</v>
       </c>
       <c r="F2080" t="n">
         <v>1.174877591903893</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.022533796223849</v>
+        <v>4.890806886280281</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.64790116312026</v>
+        <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.33462865430316</v>
+        <v>4.185880331137945</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.899192169498532</v>
+        <v>-4.758806955585109</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.37459536219</v>
+        <v>2.282001124590153</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.035440801108509</v>
+        <v>1.174877591903893</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.955893134968266</v>
+        <v>4.890806886280281</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881059287042963</v>
+        <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.347356262284253</v>
+        <v>4.198607939119037</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.056260627754156</v>
+        <v>-4.915875413840732</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.324495586868842</v>
+        <v>2.231901349268996</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.035440801108509</v>
+        <v>1.174877591903893</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.968620742949359</v>
+        <v>4.903534494261373</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717065078804107</v>
+        <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.34930226070864</v>
+        <v>4.200553937543424</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.050268380965345</v>
+        <v>-4.909883167051921</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.328838484008755</v>
+        <v>2.236244246408909</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.035440801108509</v>
+        <v>1.174877591903893</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.970566741373746</v>
+        <v>4.90548049268576</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741936267528556</v>
+        <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.342956396726409</v>
+        <v>4.194208073561193</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.961710419834577</v>
+        <v>-4.821325205921153</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.35791580447883</v>
+        <v>2.265321566878984</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.035440801108509</v>
+        <v>1.174877591903893</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.964220877391515</v>
+        <v>4.899134628703529</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735294641762429</v>
+        <v>3.735300721383091</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.342265074165405</v>
+        <v>4.193516751000189</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.943951342331503</v>
+        <v>-4.803566128418079</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.364328112919056</v>
+        <v>2.271733875319209</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.035440801108509</v>
+        <v>1.174877591903893</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.96352955483051</v>
+        <v>4.898443306142525</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778226068100335</v>
+        <v>3.778232147720997</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.355047260073992</v>
+        <v>4.206298936908776</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.844321191282435</v>
+        <v>-4.703935977369011</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.41696235924727</v>
+        <v>2.324368121647423</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.135070952157576</v>
+        <v>1.274507742952961</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.036089831368537</v>
+        <v>4.971003582680552</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775351017834609</v>
+        <v>3.775357097455271</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.544201525572718</v>
+        <v>4.395453202407502</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.893720699971446</v>
+        <v>-4.753335486058022</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.586356821270392</v>
+        <v>2.493762583670545</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.145329785589321</v>
+        <v>1.284766576384706</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.231399396926311</v>
+        <v>5.166313148238325</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.74907197934247</v>
+        <v>3.749078058963132</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.53139019867558</v>
+        <v>4.382641875510364</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.68703622632907</v>
+        <v>-4.546651012415646</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.656219283830204</v>
+        <v>2.563625046230358</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.352014259231697</v>
+        <v>1.491451050027081</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.342598754214598</v>
+        <v>5.277512505526613</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.74027830954188</v>
+        <v>3.740284389162542</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.533391712329685</v>
+        <v>4.384643389164469</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.721193121326596</v>
+        <v>-4.580807907413172</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.644558039485299</v>
+        <v>2.551963801885452</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.268430489690884</v>
+        <v>1.407867280486269</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.294450006144216</v>
+        <v>5.22936375745623</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782476036031721</v>
+        <v>3.782482115652382</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.886888826319352</v>
+        <v>4.738140503154137</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.62860364226514</v>
+        <v>-4.488218428351716</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.035090945099548</v>
+        <v>2.942496707499703</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.268430489690884</v>
+        <v>1.407867280486269</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.647947120133884</v>
+        <v>5.582860871445898</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809049825488009</v>
+        <v>3.809055905108671</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.891451937886456</v>
+        <v>4.74270361472124</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.68849227008869</v>
+        <v>-4.548107056175266</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.015698605537232</v>
+        <v>2.923104367937385</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.25430857500342</v>
+        <v>1.393745365798804</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.644037082888508</v>
+        <v>5.578950834200523</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.8351963614829</v>
+        <v>3.835202441103561</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.941281879209984</v>
+        <v>4.792533556044767</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.636275960292348</v>
+        <v>-4.495890746378924</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.086415070779297</v>
+        <v>2.993820833179449</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.25430857500342</v>
+        <v>1.393745365798804</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.693867024212036</v>
+        <v>5.62878077552405</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821821067427082</v>
+        <v>3.821827147047744</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.950095849419995</v>
+        <v>4.801347526254778</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.604378443207103</v>
+        <v>-4.463993229293679</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.107988047823406</v>
+        <v>3.015393810223559</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.286206092088665</v>
+        <v>1.42564288288405</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.721819504673194</v>
+        <v>5.656733255985208</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825262337030091</v>
+        <v>3.825268416650752</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.945733433459192</v>
+        <v>4.796985110293975</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.619133767407243</v>
+        <v>-4.478748553493819</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.097723502182546</v>
+        <v>3.005129264582699</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.286206092088665</v>
+        <v>1.42564288288405</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.717457088712392</v>
+        <v>5.652370840024405</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845038586515086</v>
+        <v>3.845044666135747</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.936657936875472</v>
+        <v>4.787909613710255</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.569669144037332</v>
+        <v>-4.429283930123908</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.108433854946791</v>
+        <v>3.015839617346944</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.335670715458577</v>
+        <v>1.475107506253962</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.738060366150618</v>
+        <v>5.672974117462632</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.825925710858559</v>
+        <v>3.82593179047922</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.933065604590406</v>
+        <v>4.78431728142519</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.406561151883716</v>
+        <v>-4.266175937970292</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.170084719523172</v>
+        <v>3.077490481923324</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.498778707612192</v>
+        <v>1.638215498407577</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.832332829157721</v>
+        <v>5.767246580469735</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,45 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.844270077764273</v>
+        <v>3.847096478844247</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.942112641281534</v>
+        <v>4.793364318116318</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.27375352638655</v>
+        <v>-4.133368312473126</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.232254806413167</v>
+        <v>3.139660568813319</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.498778707612192</v>
+        <v>1.638215498407577</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.84137986584885</v>
+        <v>5.776293617160864</v>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" s="2" t="n">
+        <v>45560</v>
+      </c>
+      <c r="B2098" t="n">
+        <v>3.648254281953492</v>
+      </c>
+      <c r="C2098" t="n">
+        <v>4.986769173343098</v>
+      </c>
+      <c r="D2098" t="n">
+        <v>-4.009019082087336</v>
+      </c>
+      <c r="E2098" t="n">
+        <v>3.382805116194415</v>
+      </c>
+      <c r="F2098" t="n">
+        <v>1.762564728793366</v>
+      </c>
+      <c r="G2098" t="n">
+        <v>6.044308010619117</v>
       </c>
     </row>
   </sheetData>
